--- a/2026/PATXOT 512/ENERO/PATXOT 521 Enero.xlsx
+++ b/2026/PATXOT 512/ENERO/PATXOT 521 Enero.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\PATXOT 512\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\PATXOT 512\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3FED3BB-C5AC-4AF2-8B7A-6E97A95AF5FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032F868F-83D7-4DF6-B625-B0AA12AB3A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-210" yWindow="15" windowWidth="15375" windowHeight="7230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -23,6 +23,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$L$16</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -318,7 +323,7 @@
   <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -1082,17 +1087,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1110,9 +1112,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1123,61 +1122,19 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1"/>
@@ -1188,13 +1145,61 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="9" fillId="3" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="9" fillId="3" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="9" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1276,9 +1281,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1316,9 +1321,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1351,9 +1356,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1386,9 +1408,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1649,10 +1688,10 @@
       <c r="B17" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="91">
+      <c r="C17" s="90">
         <v>35799</v>
       </c>
-      <c r="D17" s="92"/>
+      <c r="D17" s="91"/>
       <c r="F17" s="7"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1669,7 +1708,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="41"/>
-      <c r="C19" s="93"/>
+      <c r="C19" s="92"/>
       <c r="D19" s="26"/>
     </row>
     <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -1700,7 +1739,7 @@
       </c>
       <c r="B22" s="41"/>
       <c r="C22" s="39"/>
-      <c r="D22" s="94"/>
+      <c r="D22" s="93"/>
       <c r="E22" s="7"/>
       <c r="F22" s="13"/>
     </row>
@@ -1855,50 +1894,50 @@
       <c r="C42" s="11"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="90" t="str">
+      <c r="A43" s="119" t="str">
         <f>'prorrateo '!A16:L16</f>
         <v>Atención: se han reliquidado todas las deudas correspondientes a cada unidad funcional, dejando reflejados los saldos reales de cada una.
 A partir de este mes se aplicarán intereses a quienes no abonen las expensas en tiempo y forma.
 La columna Ingresos registra pagos efectuados tanto durante el mes de enero como en meses anteriores. Por este motivo, en la caja general se han descontado aquellos pagos que no corresponden al período liquidado, a fin de evitar su doble contabilización, ya que los mismos fueron imputados oportunamente en expensas anteriores.
 Del mismo modo, los saldos anteriores incluyen montos correspondientes a expensas adeudadas no solo del mes de diciembre, sino también de meses posteriores.</v>
       </c>
-      <c r="B43" s="90"/>
-      <c r="C43" s="90"/>
+      <c r="B43" s="119"/>
+      <c r="C43" s="119"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="90"/>
-      <c r="B44" s="90"/>
-      <c r="C44" s="90"/>
+      <c r="A44" s="119"/>
+      <c r="B44" s="119"/>
+      <c r="C44" s="119"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="90"/>
-      <c r="B45" s="90"/>
-      <c r="C45" s="90"/>
+      <c r="A45" s="119"/>
+      <c r="B45" s="119"/>
+      <c r="C45" s="119"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="90"/>
-      <c r="B46" s="90"/>
-      <c r="C46" s="90"/>
+      <c r="A46" s="119"/>
+      <c r="B46" s="119"/>
+      <c r="C46" s="119"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="90"/>
-      <c r="B47" s="90"/>
-      <c r="C47" s="90"/>
+      <c r="A47" s="119"/>
+      <c r="B47" s="119"/>
+      <c r="C47" s="119"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="90"/>
-      <c r="B48" s="90"/>
-      <c r="C48" s="90"/>
+      <c r="A48" s="119"/>
+      <c r="B48" s="119"/>
+      <c r="C48" s="119"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="90"/>
-      <c r="B49" s="90"/>
-      <c r="C49" s="90"/>
+      <c r="A49" s="119"/>
+      <c r="B49" s="119"/>
+      <c r="C49" s="119"/>
     </row>
     <row r="50" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="90"/>
-      <c r="B50" s="90"/>
-      <c r="C50" s="90"/>
+      <c r="A50" s="119"/>
+      <c r="B50" s="119"/>
+      <c r="C50" s="119"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="10"/>
@@ -2008,10 +2047,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="97"/>
+      <c r="B1" s="96"/>
       <c r="C1" s="26"/>
       <c r="D1" s="26"/>
       <c r="E1" s="27">
@@ -2019,10 +2058,10 @@
       </c>
       <c r="F1" s="26"/>
       <c r="G1" s="26"/>
-      <c r="H1" s="98" t="s">
+      <c r="H1" s="135" t="s">
         <v>83</v>
       </c>
-      <c r="I1" s="98"/>
+      <c r="I1" s="135"/>
       <c r="J1" s="27">
         <v>159017.97</v>
       </c>
@@ -2030,83 +2069,83 @@
       <c r="L1" s="26"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="99">
+      <c r="A2" s="97">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
       </c>
-      <c r="B2" s="100"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="103"/>
-      <c r="L2" s="104"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="102"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="105" t="s">
+      <c r="A3" s="129" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="107" t="s">
+      <c r="B3" s="130"/>
+      <c r="C3" s="125" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="108" t="s">
+      <c r="D3" s="127" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="109" t="s">
+      <c r="E3" s="103" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="109" t="s">
+      <c r="F3" s="103" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="107" t="s">
+      <c r="G3" s="125" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="107" t="s">
+      <c r="H3" s="125" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="110" t="s">
+      <c r="I3" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="111" t="s">
+      <c r="J3" s="133" t="s">
         <v>80</v>
       </c>
-      <c r="K3" s="107" t="s">
+      <c r="K3" s="125" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="112" t="s">
+      <c r="L3" s="104" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="113"/>
-      <c r="B4" s="114"/>
-      <c r="C4" s="115"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="117" t="s">
+      <c r="A4" s="131"/>
+      <c r="B4" s="132"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="128"/>
+      <c r="E4" s="105" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="109" t="s">
+      <c r="F4" s="103" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="119"/>
-      <c r="K4" s="115"/>
-      <c r="L4" s="120" t="s">
+      <c r="G4" s="126"/>
+      <c r="H4" s="126"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="134"/>
+      <c r="K4" s="126"/>
+      <c r="L4" s="106" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="121">
+      <c r="A5" s="123">
         <v>1</v>
       </c>
-      <c r="B5" s="122"/>
+      <c r="B5" s="124"/>
       <c r="C5" s="48" t="s">
         <v>37</v>
       </c>
@@ -2118,36 +2157,36 @@
         <f>E5</f>
         <v>46673.998480000002</v>
       </c>
-      <c r="G5" s="123">
+      <c r="G5" s="107">
         <f>E5-F5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="123">
+      <c r="H5" s="107">
         <f>IF(G5&gt;0,G5*6%,0)</f>
         <v>0</v>
       </c>
       <c r="I5" s="39">
         <v>13.8</v>
       </c>
-      <c r="J5" s="124">
+      <c r="J5" s="108">
         <f>E$1*I5/100</f>
         <v>15088.036800000002</v>
       </c>
-      <c r="K5" s="125">
+      <c r="K5" s="109">
         <f>edesur!H5</f>
         <v>9493.6101492537327</v>
       </c>
-      <c r="L5" s="126">
+      <c r="L5" s="110">
         <f>G5+H5+J5+K5</f>
         <v>24581.646949253736</v>
       </c>
       <c r="M5" s="89"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="121">
+      <c r="A6" s="123">
         <v>2</v>
       </c>
-      <c r="B6" s="122"/>
+      <c r="B6" s="124"/>
       <c r="C6" s="48" t="s">
         <v>38</v>
       </c>
@@ -2156,35 +2195,35 @@
         <v>93174.074720303732</v>
       </c>
       <c r="F6" s="86"/>
-      <c r="G6" s="123">
+      <c r="G6" s="107">
         <f t="shared" ref="G6:G14" si="0">E6-F6</f>
         <v>93174.074720303732</v>
       </c>
-      <c r="H6" s="123">
+      <c r="H6" s="107">
         <f t="shared" ref="H6:H14" si="1">IF(G6&gt;0,G6*6%,0)</f>
         <v>5590.4444832182235</v>
       </c>
       <c r="I6" s="39">
         <v>11.86</v>
       </c>
-      <c r="J6" s="124">
+      <c r="J6" s="108">
         <f t="shared" ref="J6:J14" si="2">E$1*I6/100</f>
         <v>12966.964960000001</v>
       </c>
-      <c r="K6" s="125">
+      <c r="K6" s="109">
         <f>edesur!H6</f>
         <v>46518.689731343286</v>
       </c>
-      <c r="L6" s="126">
+      <c r="L6" s="110">
         <f t="shared" ref="L6:L14" si="3">G6+H6+J6+K6</f>
         <v>158250.17389486523</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="121">
+      <c r="A7" s="123">
         <v>3</v>
       </c>
-      <c r="B7" s="122"/>
+      <c r="B7" s="124"/>
       <c r="C7" s="48" t="s">
         <v>38</v>
       </c>
@@ -2199,35 +2238,35 @@
         <f>120000+50000+114600</f>
         <v>284600</v>
       </c>
-      <c r="G7" s="123">
+      <c r="G7" s="107">
         <f t="shared" si="0"/>
         <v>164463.16999999998</v>
       </c>
-      <c r="H7" s="123">
+      <c r="H7" s="107">
         <f t="shared" si="1"/>
         <v>9867.7901999999995</v>
       </c>
       <c r="I7" s="39">
         <v>12.46</v>
       </c>
-      <c r="J7" s="124">
+      <c r="J7" s="108">
         <f t="shared" si="2"/>
         <v>13622.966560000003</v>
       </c>
-      <c r="K7" s="125">
+      <c r="K7" s="109">
         <f>edesur!H7</f>
         <v>46044.009223880596</v>
       </c>
-      <c r="L7" s="126">
+      <c r="L7" s="110">
         <f t="shared" si="3"/>
         <v>233997.93598388057</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="121">
+      <c r="A8" s="123">
         <v>4</v>
       </c>
-      <c r="B8" s="122"/>
+      <c r="B8" s="124"/>
       <c r="C8" s="48" t="s">
         <v>39</v>
       </c>
@@ -2242,35 +2281,35 @@
         <f>128678+49000+128000</f>
         <v>305678</v>
       </c>
-      <c r="G8" s="123">
+      <c r="G8" s="107">
         <f t="shared" si="0"/>
         <v>209871.78000000003</v>
       </c>
-      <c r="H8" s="123">
+      <c r="H8" s="107">
         <f t="shared" si="1"/>
         <v>12592.306800000002</v>
       </c>
       <c r="I8" s="39">
         <v>14.75</v>
       </c>
-      <c r="J8" s="124">
+      <c r="J8" s="108">
         <f t="shared" si="2"/>
         <v>16126.706</v>
       </c>
-      <c r="K8" s="125">
+      <c r="K8" s="109">
         <f>edesur!H8</f>
         <v>9493.6101492537327</v>
       </c>
-      <c r="L8" s="126">
+      <c r="L8" s="110">
         <f t="shared" si="3"/>
         <v>248084.40294925377</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="121">
+      <c r="A9" s="123">
         <v>5</v>
       </c>
-      <c r="B9" s="122"/>
+      <c r="B9" s="124"/>
       <c r="C9" s="48" t="s">
         <v>40</v>
       </c>
@@ -2285,35 +2324,35 @@
         <f>145436.21+54367.43+65136</f>
         <v>264939.64</v>
       </c>
-      <c r="G9" s="123">
+      <c r="G9" s="107">
         <f t="shared" si="0"/>
         <v>-8.0000000016298145E-2</v>
       </c>
-      <c r="H9" s="123">
+      <c r="H9" s="107">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I9" s="39">
         <v>12.41</v>
       </c>
-      <c r="J9" s="124">
+      <c r="J9" s="108">
         <f t="shared" si="2"/>
         <v>13568.29976</v>
       </c>
-      <c r="K9" s="125">
+      <c r="K9" s="109">
         <f>edesur!H9</f>
         <v>28480.830447761193</v>
       </c>
-      <c r="L9" s="126">
+      <c r="L9" s="110">
         <f>G9+H9+J9+K9</f>
         <v>42049.050207761175</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="121">
+      <c r="A10" s="123">
         <v>6</v>
       </c>
-      <c r="B10" s="122"/>
+      <c r="B10" s="124"/>
       <c r="C10" s="48" t="s">
         <v>41</v>
       </c>
@@ -2326,35 +2365,35 @@
         <f>4150+26423+54675+85000+44601-F14</f>
         <v>169324.31</v>
       </c>
-      <c r="G10" s="123">
+      <c r="G10" s="107">
         <f t="shared" si="0"/>
         <v>274585.02</v>
       </c>
-      <c r="H10" s="123">
+      <c r="H10" s="107">
         <f t="shared" si="1"/>
         <v>16475.101200000001</v>
       </c>
       <c r="I10" s="39">
         <v>12.48</v>
       </c>
-      <c r="J10" s="124">
+      <c r="J10" s="108">
         <f t="shared" si="2"/>
         <v>13644.833280000003</v>
       </c>
-      <c r="K10" s="125">
+      <c r="K10" s="109">
         <f>edesur!H10</f>
         <v>9493.6101492537327</v>
       </c>
-      <c r="L10" s="126">
+      <c r="L10" s="110">
         <f t="shared" si="3"/>
         <v>314198.56462925376</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="121">
+      <c r="A11" s="123">
         <v>7</v>
       </c>
-      <c r="B11" s="122"/>
+      <c r="B11" s="124"/>
       <c r="C11" s="48" t="s">
         <v>42</v>
       </c>
@@ -2366,36 +2405,36 @@
         <f t="shared" ref="F11:F14" si="4">E11</f>
         <v>53678.783496000004</v>
       </c>
-      <c r="G11" s="123">
+      <c r="G11" s="107">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H11" s="123">
+      <c r="H11" s="107">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I11" s="39">
         <v>18.260000000000002</v>
       </c>
-      <c r="J11" s="124">
+      <c r="J11" s="108">
         <f t="shared" si="2"/>
         <v>19964.315360000004</v>
       </c>
-      <c r="K11" s="125">
+      <c r="K11" s="109">
         <f>edesur!H11</f>
         <v>9493.6101492537327</v>
       </c>
-      <c r="L11" s="126">
+      <c r="L11" s="110">
         <f t="shared" si="3"/>
         <v>29457.925509253735</v>
       </c>
       <c r="M11" s="89"/>
     </row>
     <row r="12" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="121" t="s">
+      <c r="A12" s="123" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="122"/>
+      <c r="B12" s="124"/>
       <c r="C12" s="48" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
@@ -2411,32 +2450,32 @@
         <f>44137.05+2105</f>
         <v>46242.05</v>
       </c>
-      <c r="G12" s="123">
+      <c r="G12" s="107">
         <f t="shared" si="0"/>
         <v>-0.41999999999825377</v>
       </c>
-      <c r="H12" s="123">
+      <c r="H12" s="107">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I12" s="39">
         <v>1.34</v>
       </c>
-      <c r="J12" s="124">
+      <c r="J12" s="108">
         <f t="shared" si="2"/>
         <v>1465.07024</v>
       </c>
-      <c r="K12" s="125"/>
-      <c r="L12" s="126">
+      <c r="K12" s="109"/>
+      <c r="L12" s="110">
         <f t="shared" si="3"/>
         <v>1464.6502400000018</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="121" t="s">
+      <c r="A13" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="122"/>
+      <c r="B13" s="124"/>
       <c r="C13" s="48" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -2446,32 +2485,32 @@
         <v>41426.1</v>
       </c>
       <c r="F13" s="86"/>
-      <c r="G13" s="123">
+      <c r="G13" s="107">
         <f t="shared" si="0"/>
         <v>41426.1</v>
       </c>
-      <c r="H13" s="123">
+      <c r="H13" s="107">
         <f t="shared" si="1"/>
         <v>2485.5659999999998</v>
       </c>
       <c r="I13" s="39">
         <v>1.32</v>
       </c>
-      <c r="J13" s="124">
+      <c r="J13" s="108">
         <f t="shared" si="2"/>
         <v>1443.20352</v>
       </c>
-      <c r="K13" s="125"/>
-      <c r="L13" s="126">
+      <c r="K13" s="109"/>
+      <c r="L13" s="110">
         <f t="shared" si="3"/>
         <v>45354.86952</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="121" t="s">
+      <c r="A14" s="123" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="122"/>
+      <c r="B14" s="124"/>
       <c r="C14" s="24" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -2487,82 +2526,86 @@
         <f t="shared" si="4"/>
         <v>45524.69</v>
       </c>
-      <c r="G14" s="123">
+      <c r="G14" s="107">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="123">
+      <c r="H14" s="107">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I14" s="39">
         <v>1.32</v>
       </c>
-      <c r="J14" s="124">
+      <c r="J14" s="108">
         <f t="shared" si="2"/>
         <v>1443.20352</v>
       </c>
-      <c r="K14" s="125"/>
-      <c r="L14" s="126">
+      <c r="K14" s="109"/>
+      <c r="L14" s="110">
         <f t="shared" si="3"/>
         <v>1443.20352</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="127" t="s">
+      <c r="A15" s="111" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="128"/>
-      <c r="C15" s="129"/>
-      <c r="D15" s="129"/>
-      <c r="E15" s="130">
+      <c r="B15" s="112"/>
+      <c r="C15" s="113"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="114">
         <f>SUM(E5:E14)</f>
         <v>2000181.1166963042</v>
       </c>
-      <c r="F15" s="131">
+      <c r="F15" s="115">
         <f>SUM(F5:F14)</f>
         <v>1216661.4719760001</v>
       </c>
-      <c r="G15" s="131"/>
-      <c r="H15" s="132">
+      <c r="G15" s="115"/>
+      <c r="H15" s="116">
         <f>SUM(H5:H14)</f>
         <v>47011.208683218225</v>
       </c>
-      <c r="I15" s="133">
+      <c r="I15" s="117">
         <f t="shared" ref="I15" si="5">SUM(I5:I14)</f>
         <v>100</v>
       </c>
-      <c r="J15" s="134">
+      <c r="J15" s="118">
         <f>SUM(J5:J14)</f>
         <v>109333.6</v>
       </c>
-      <c r="K15" s="130">
+      <c r="K15" s="114">
         <f>SUM(K5:K11)</f>
         <v>159017.97</v>
       </c>
-      <c r="L15" s="130">
+      <c r="L15" s="114">
         <f>SUM(L5:L14)</f>
         <v>1098882.423403522</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="217.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="135" t="s">
+      <c r="A16" s="120" t="s">
         <v>91</v>
       </c>
-      <c r="B16" s="135"/>
-      <c r="C16" s="135"/>
-      <c r="D16" s="135"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135"/>
-      <c r="I16" s="135"/>
-      <c r="J16" s="135"/>
-      <c r="K16" s="135"/>
-      <c r="L16" s="135"/>
+      <c r="B16" s="120"/>
+      <c r="C16" s="120"/>
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="120"/>
+      <c r="I16" s="120"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="H1:I1"/>
     <mergeCell ref="A16:L16"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="A6:B6"/>
@@ -2579,10 +2622,6 @@
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2920,7 +2959,7 @@
         <v>100.00000000000003</v>
       </c>
       <c r="G12" s="26"/>
-      <c r="H12" s="95">
+      <c r="H12" s="94">
         <f>SUM(H5:H11)</f>
         <v>159017.97</v>
       </c>
